--- a/new_folder/columns_group.xlsx
+++ b/new_folder/columns_group.xlsx
@@ -9,17 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12390" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12390"/>
   </bookViews>
   <sheets>
-    <sheet name="GROUP" sheetId="1" r:id="rId1"/>
-    <sheet name="table_od" sheetId="3" r:id="rId2"/>
-    <sheet name="merge_keys" sheetId="4" r:id="rId3"/>
-    <sheet name="funct_map" sheetId="5" r:id="rId4"/>
-    <sheet name="API" sheetId="2" r:id="rId5"/>
+    <sheet name="group" sheetId="1" r:id="rId1"/>
+    <sheet name="API" sheetId="2" r:id="rId2"/>
+    <sheet name="fin_invest_tables" sheetId="6" r:id="rId3"/>
+    <sheet name="table_od" sheetId="3" r:id="rId4"/>
+    <sheet name="merge_keys" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GROUP!$A$2:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">group!$A$2:$B$8</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,69 +31,591 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
-  <si>
-    <t>CASH</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="212">
+  <si>
+    <t>OD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FIN</t>
+    <t>KEYS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DEBT</t>
+    <t>coid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CLOSE</t>
+    <t>mdate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ROI</t>
+    <t>coid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MONTHLY_REVENUE</t>
+    <t>all_dates</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MON</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大戶持股比率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>column_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>group</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>group_set</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>API_code</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三大法人買賣超</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MKT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALT</t>
+    <t>coid</t>
+  </si>
+  <si>
+    <t>fin_self_acc</t>
+  </si>
+  <si>
+    <t>mdate</t>
+  </si>
+  <si>
+    <t>key3</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>sem</t>
+  </si>
+  <si>
+    <t>fin_type</t>
+  </si>
+  <si>
+    <t>curr</t>
+  </si>
+  <si>
+    <t>annd</t>
+  </si>
+  <si>
+    <t>fin_ind</t>
+  </si>
+  <si>
+    <t>ip12</t>
+  </si>
+  <si>
+    <t>gm</t>
+  </si>
+  <si>
+    <t>isoi</t>
+  </si>
+  <si>
+    <t>isibt</t>
+  </si>
+  <si>
+    <t>isni</t>
+  </si>
+  <si>
+    <t>isnip</t>
+  </si>
+  <si>
+    <t>r306</t>
+  </si>
+  <si>
+    <t>eps</t>
+  </si>
+  <si>
+    <t>r105</t>
+  </si>
+  <si>
+    <t>r106</t>
+  </si>
+  <si>
+    <t>r107</t>
+  </si>
+  <si>
+    <t>r108</t>
+  </si>
+  <si>
+    <t>r401</t>
+  </si>
+  <si>
+    <t>r402</t>
+  </si>
+  <si>
+    <t>r403</t>
+  </si>
+  <si>
+    <t>r404</t>
+  </si>
+  <si>
+    <t>r405</t>
+  </si>
+  <si>
+    <t>fin_board_select</t>
+  </si>
+  <si>
+    <t>fin_auditor</t>
+  </si>
+  <si>
+    <t>stk_price</t>
+  </si>
+  <si>
+    <t>mkt</t>
+  </si>
+  <si>
+    <t>open_d</t>
+  </si>
+  <si>
+    <t>high_d</t>
+  </si>
+  <si>
+    <t>low_d</t>
+  </si>
+  <si>
+    <t>close_d</t>
+  </si>
+  <si>
+    <t>adjfac</t>
+  </si>
+  <si>
+    <t>vol</t>
+  </si>
+  <si>
+    <t>amt</t>
+  </si>
+  <si>
+    <t>trn</t>
+  </si>
+  <si>
+    <t>bid</t>
+  </si>
+  <si>
+    <t>offer</t>
+  </si>
+  <si>
+    <t>avgprc</t>
+  </si>
+  <si>
+    <t>roi</t>
+  </si>
+  <si>
+    <t>hmlpct</t>
+  </si>
+  <si>
+    <t>turnover</t>
+  </si>
+  <si>
+    <t>shares</t>
+  </si>
+  <si>
+    <t>mktcap</t>
+  </si>
+  <si>
+    <t>mktcap_pct</t>
+  </si>
+  <si>
+    <t>amt_pct</t>
+  </si>
+  <si>
+    <t>per</t>
+  </si>
+  <si>
+    <t>pbr</t>
+  </si>
+  <si>
+    <t>div_yid</t>
+  </si>
+  <si>
+    <t>cdiv_yid</t>
+  </si>
+  <si>
+    <t>month_sales</t>
+  </si>
+  <si>
+    <t>annd_s</t>
+  </si>
+  <si>
+    <t>d0001</t>
+  </si>
+  <si>
+    <t>d0002</t>
+  </si>
+  <si>
+    <t>d0003</t>
+  </si>
+  <si>
+    <t>d0004</t>
+  </si>
+  <si>
+    <t>d0005</t>
+  </si>
+  <si>
+    <t>d0006</t>
+  </si>
+  <si>
+    <t>d0007</t>
+  </si>
+  <si>
+    <t>a4maxh</t>
+  </si>
+  <si>
+    <t>a4maxd</t>
+  </si>
+  <si>
+    <t>a4max_pct</t>
+  </si>
+  <si>
+    <t>a4minh</t>
+  </si>
+  <si>
+    <t>a4mind</t>
+  </si>
+  <si>
+    <t>a4min_pct</t>
+  </si>
+  <si>
+    <t>a4hfg</t>
+  </si>
+  <si>
+    <t>a4yfg</t>
+  </si>
+  <si>
+    <t>a4mfg</t>
+  </si>
+  <si>
+    <t>sl_month</t>
+  </si>
+  <si>
+    <t>t8107</t>
+  </si>
+  <si>
+    <t>t8111</t>
+  </si>
+  <si>
+    <t>r18</t>
+  </si>
+  <si>
+    <t>t8133</t>
+  </si>
+  <si>
+    <t>t8134</t>
+  </si>
+  <si>
+    <t>r25</t>
+  </si>
+  <si>
+    <t>r26</t>
+  </si>
+  <si>
+    <t>r26a</t>
+  </si>
+  <si>
+    <t>d0025</t>
+  </si>
+  <si>
+    <t>d0026</t>
+  </si>
+  <si>
+    <t>d0027</t>
+  </si>
+  <si>
+    <t>r19</t>
+  </si>
+  <si>
+    <t>r27</t>
+  </si>
+  <si>
+    <t>bargaing_chips</t>
+  </si>
+  <si>
+    <t>qfii_buy</t>
+  </si>
+  <si>
+    <t>qfii_sell</t>
+  </si>
+  <si>
+    <t>qfii_ex</t>
+  </si>
+  <si>
+    <t>qfii_bamt</t>
+  </si>
+  <si>
+    <t>qfii_samt</t>
+  </si>
+  <si>
+    <t>qfii_examt</t>
+  </si>
+  <si>
+    <t>qfii_pct</t>
+  </si>
+  <si>
+    <t>fund_buy</t>
+  </si>
+  <si>
+    <t>fund_sell</t>
+  </si>
+  <si>
+    <t>fund_ex</t>
+  </si>
+  <si>
+    <t>fund_bamt</t>
+  </si>
+  <si>
+    <t>fund_samt</t>
+  </si>
+  <si>
+    <t>fund_examt</t>
+  </si>
+  <si>
+    <t>fd_pct</t>
+  </si>
+  <si>
+    <t>dlrp_buy</t>
+  </si>
+  <si>
+    <t>dlrp_sell</t>
+  </si>
+  <si>
+    <t>dlrp_ex</t>
+  </si>
+  <si>
+    <t>dlrp_bamt</t>
+  </si>
+  <si>
+    <t>dlrp_samt</t>
+  </si>
+  <si>
+    <t>dlrp_examt</t>
+  </si>
+  <si>
+    <t>dlrh_buy</t>
+  </si>
+  <si>
+    <t>dlrh_sell</t>
+  </si>
+  <si>
+    <t>dlrh_ex</t>
+  </si>
+  <si>
+    <t>dlrh_bamt</t>
+  </si>
+  <si>
+    <t>dlrh_samt</t>
+  </si>
+  <si>
+    <t>dlrh_examt</t>
+  </si>
+  <si>
+    <t>dlr_pct</t>
+  </si>
+  <si>
+    <t>tot_buy</t>
+  </si>
+  <si>
+    <t>tot_sell</t>
+  </si>
+  <si>
+    <t>tot_ex</t>
+  </si>
+  <si>
+    <t>tot_bamt</t>
+  </si>
+  <si>
+    <t>tot_samt</t>
+  </si>
+  <si>
+    <t>tot_examt</t>
+  </si>
+  <si>
+    <t>buy_l</t>
+  </si>
+  <si>
+    <t>sell_l</t>
+  </si>
+  <si>
+    <t>long_t</t>
+  </si>
+  <si>
+    <t>long_ta</t>
+  </si>
+  <si>
+    <t>cash_l</t>
+  </si>
+  <si>
+    <t>limit_l</t>
+  </si>
+  <si>
+    <t>buy_s</t>
+  </si>
+  <si>
+    <t>sell_s</t>
+  </si>
+  <si>
+    <t>short_t</t>
+  </si>
+  <si>
+    <t>short_ta</t>
+  </si>
+  <si>
+    <t>pay_s</t>
+  </si>
+  <si>
+    <t>limit_s</t>
+  </si>
+  <si>
+    <t>s_l_pct</t>
+  </si>
+  <si>
+    <t>offset_r</t>
+  </si>
+  <si>
+    <t>offset_a</t>
+  </si>
+  <si>
+    <t>sale_b1</t>
+  </si>
+  <si>
+    <t>sale_b1a</t>
+  </si>
+  <si>
+    <t>returns</t>
+  </si>
+  <si>
+    <t>borr_t1</t>
+  </si>
+  <si>
+    <t>borr_t1a</t>
+  </si>
+  <si>
+    <t>limit_b1</t>
+  </si>
+  <si>
+    <t>lmr</t>
+  </si>
+  <si>
+    <t>smr</t>
+  </si>
+  <si>
+    <t>tmr</t>
+  </si>
+  <si>
+    <t>vol_dt</t>
+  </si>
+  <si>
+    <t>vol_dtp</t>
+  </si>
+  <si>
+    <t>share_distribution</t>
+  </si>
+  <si>
+    <t>edate1</t>
+  </si>
+  <si>
+    <t>fc_s</t>
+  </si>
+  <si>
+    <t>pledg_s</t>
+  </si>
+  <si>
+    <t>edate2</t>
+  </si>
+  <si>
+    <t>shrm_u400</t>
+  </si>
+  <si>
+    <t>shrs_u400</t>
+  </si>
+  <si>
+    <t>shrp_u400</t>
+  </si>
+  <si>
+    <t>shrm_o400</t>
+  </si>
+  <si>
+    <t>shrs_o400</t>
+  </si>
+  <si>
+    <t>shrp_o400</t>
+  </si>
+  <si>
+    <t>shrm_4_6</t>
+  </si>
+  <si>
+    <t>shrs_4_6</t>
+  </si>
+  <si>
+    <t>shrp_4_6</t>
+  </si>
+  <si>
+    <t>shrm_6_8</t>
+  </si>
+  <si>
+    <t>shrs_6_8</t>
+  </si>
+  <si>
+    <t>shrp_6_8</t>
+  </si>
+  <si>
+    <t>shrm_8_10</t>
+  </si>
+  <si>
+    <t>shrs_8_10</t>
+  </si>
+  <si>
+    <t>shrp_8_10</t>
+  </si>
+  <si>
+    <t>shrm_o1000</t>
+  </si>
+  <si>
+    <t>shrs_o1000</t>
+  </si>
+  <si>
+    <t>shrp_o1000</t>
+  </si>
+  <si>
+    <t>stk_attr</t>
+  </si>
+  <si>
+    <t>mkt_bd</t>
+  </si>
+  <si>
+    <t>industry_c</t>
+  </si>
+  <si>
+    <t>industry_e</t>
+  </si>
+  <si>
+    <t>atten_fg</t>
+  </si>
+  <si>
+    <t>disp_fg</t>
+  </si>
+  <si>
+    <t>mch_prd</t>
+  </si>
+  <si>
+    <t>susp_fg</t>
+  </si>
+  <si>
+    <t>full_fg</t>
+  </si>
+  <si>
+    <t>limit_fg</t>
+  </si>
+  <si>
+    <t>limo_fg</t>
+  </si>
+  <si>
+    <t>sbadt_fg</t>
+  </si>
+  <si>
+    <t>idx_twn50</t>
+  </si>
+  <si>
+    <t>idx_msci</t>
+  </si>
+  <si>
+    <t>idx_otc50</t>
+  </si>
+  <si>
+    <t>idx_otc200</t>
+  </si>
+  <si>
+    <t>idx_hdiv</t>
+  </si>
+  <si>
+    <t>idx_mcap</t>
+  </si>
+  <si>
+    <t>fin_board_select</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -105,47 +627,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FIN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MKT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MON</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A0003</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A0004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A0005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FIN, MKT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FIN, MON</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">FIN, </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TABLE_NAME</t>
+    <t>TABLE_NAMES</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -153,63 +639,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>fin_data</t>
+    <t>COLUMNS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stk_price</t>
+    <t>TABLE_NAMES</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>overbought</t>
+    <t>TABLE_NAMES</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>monthly_rev</t>
+    <t>API_TABLE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>share_dist</t>
+    <t>TWN/AFESTM1</t>
+  </si>
+  <si>
+    <t>TWN/AFESTMD</t>
+  </si>
+  <si>
+    <t>TWN/AINVFINQ</t>
+  </si>
+  <si>
+    <t>TWN/APIPRCD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OD</t>
+    <t>TWN/APISALE</t>
+  </si>
+  <si>
+    <t>TWN/APISHRACT</t>
+  </si>
+  <si>
+    <t>TWN/APISHRACTW</t>
+  </si>
+  <si>
+    <t>TWN/APISTKATTR</t>
+  </si>
+  <si>
+    <t>fin_auditor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KEYS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mdate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>all_dates</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COMBINATIONS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FUNCT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(1,1)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(2,2)</t>
+    <t>API_CODE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -540,83 +1015,1966 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B244"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>198</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>49</v>
+      </c>
+      <c r="B69" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>50</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>51</v>
+      </c>
+      <c r="B71" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>57</v>
+      </c>
+      <c r="B77" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>58</v>
+      </c>
+      <c r="B78" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>60</v>
+      </c>
+      <c r="B81" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>66</v>
+      </c>
+      <c r="B87" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>68</v>
+      </c>
+      <c r="B89" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>69</v>
+      </c>
+      <c r="B90" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>71</v>
+      </c>
+      <c r="B92" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>72</v>
+      </c>
+      <c r="B93" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>73</v>
+      </c>
+      <c r="B94" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>74</v>
+      </c>
+      <c r="B95" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>75</v>
+      </c>
+      <c r="B96" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>76</v>
+      </c>
+      <c r="B97" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>77</v>
+      </c>
+      <c r="B98" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>78</v>
+      </c>
+      <c r="B99" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>79</v>
+      </c>
+      <c r="B100" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>80</v>
+      </c>
+      <c r="B101" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>81</v>
+      </c>
+      <c r="B102" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>82</v>
+      </c>
+      <c r="B103" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>83</v>
+      </c>
+      <c r="B104" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>84</v>
+      </c>
+      <c r="B105" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>85</v>
+      </c>
+      <c r="B106" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>86</v>
+      </c>
+      <c r="B107" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>87</v>
+      </c>
+      <c r="B108" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>88</v>
+      </c>
+      <c r="B109" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>89</v>
+      </c>
+      <c r="B110" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>90</v>
+      </c>
+      <c r="B111" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>36</v>
+      </c>
+      <c r="B114" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>92</v>
+      </c>
+      <c r="B115" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>93</v>
+      </c>
+      <c r="B116" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>94</v>
+      </c>
+      <c r="B117" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>95</v>
+      </c>
+      <c r="B118" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>96</v>
+      </c>
+      <c r="B119" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>97</v>
+      </c>
+      <c r="B120" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>98</v>
+      </c>
+      <c r="B121" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>99</v>
+      </c>
+      <c r="B122" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>100</v>
+      </c>
+      <c r="B123" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>101</v>
+      </c>
+      <c r="B124" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>102</v>
+      </c>
+      <c r="B125" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>103</v>
+      </c>
+      <c r="B126" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>104</v>
+      </c>
+      <c r="B127" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>105</v>
+      </c>
+      <c r="B128" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>106</v>
+      </c>
+      <c r="B129" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>107</v>
+      </c>
+      <c r="B130" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>108</v>
+      </c>
+      <c r="B131" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>109</v>
+      </c>
+      <c r="B132" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>110</v>
+      </c>
+      <c r="B133" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>111</v>
+      </c>
+      <c r="B134" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>112</v>
+      </c>
+      <c r="B135" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>113</v>
+      </c>
+      <c r="B136" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>114</v>
+      </c>
+      <c r="B137" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>115</v>
+      </c>
+      <c r="B138" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>116</v>
+      </c>
+      <c r="B139" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>117</v>
+      </c>
+      <c r="B140" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>118</v>
+      </c>
+      <c r="B141" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>119</v>
+      </c>
+      <c r="B142" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>120</v>
+      </c>
+      <c r="B143" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>121</v>
+      </c>
+      <c r="B144" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>122</v>
+      </c>
+      <c r="B145" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>123</v>
+      </c>
+      <c r="B146" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>124</v>
+      </c>
+      <c r="B147" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>125</v>
+      </c>
+      <c r="B148" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>126</v>
+      </c>
+      <c r="B149" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>127</v>
+      </c>
+      <c r="B150" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>128</v>
+      </c>
+      <c r="B151" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>129</v>
+      </c>
+      <c r="B152" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>130</v>
+      </c>
+      <c r="B153" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>131</v>
+      </c>
+      <c r="B154" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>132</v>
+      </c>
+      <c r="B155" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>133</v>
+      </c>
+      <c r="B156" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>134</v>
+      </c>
+      <c r="B157" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>135</v>
+      </c>
+      <c r="B158" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>136</v>
+      </c>
+      <c r="B159" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>137</v>
+      </c>
+      <c r="B160" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>138</v>
+      </c>
+      <c r="B161" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>139</v>
+      </c>
+      <c r="B162" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>140</v>
+      </c>
+      <c r="B163" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>141</v>
+      </c>
+      <c r="B164" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>142</v>
+      </c>
+      <c r="B165" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>143</v>
+      </c>
+      <c r="B166" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>144</v>
+      </c>
+      <c r="B167" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>145</v>
+      </c>
+      <c r="B168" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>146</v>
+      </c>
+      <c r="B169" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>147</v>
+      </c>
+      <c r="B170" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>148</v>
+      </c>
+      <c r="B171" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>149</v>
+      </c>
+      <c r="B172" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>150</v>
+      </c>
+      <c r="B173" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>6</v>
+      </c>
+      <c r="B174" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>36</v>
+      </c>
+      <c r="B176" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>152</v>
+      </c>
+      <c r="B177" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>153</v>
+      </c>
+      <c r="B178" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>154</v>
+      </c>
+      <c r="B179" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>155</v>
+      </c>
+      <c r="B180" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>156</v>
+      </c>
+      <c r="B181" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>157</v>
+      </c>
+      <c r="B182" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>158</v>
+      </c>
+      <c r="B183" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>159</v>
+      </c>
+      <c r="B184" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>160</v>
+      </c>
+      <c r="B185" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>161</v>
+      </c>
+      <c r="B186" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>162</v>
+      </c>
+      <c r="B187" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>163</v>
+      </c>
+      <c r="B188" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>164</v>
+      </c>
+      <c r="B189" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>165</v>
+      </c>
+      <c r="B190" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>166</v>
+      </c>
+      <c r="B191" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>167</v>
+      </c>
+      <c r="B192" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>168</v>
+      </c>
+      <c r="B193" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>169</v>
+      </c>
+      <c r="B194" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>170</v>
+      </c>
+      <c r="B195" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>171</v>
+      </c>
+      <c r="B196" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>172</v>
+      </c>
+      <c r="B197" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>173</v>
+      </c>
+      <c r="B198" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>6</v>
+      </c>
+      <c r="B199" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>8</v>
+      </c>
+      <c r="B200" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>36</v>
+      </c>
+      <c r="B201" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>175</v>
+      </c>
+      <c r="B202" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>176</v>
+      </c>
+      <c r="B203" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>177</v>
+      </c>
+      <c r="B204" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>178</v>
+      </c>
+      <c r="B205" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>179</v>
+      </c>
+      <c r="B206" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>180</v>
+      </c>
+      <c r="B207" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>181</v>
+      </c>
+      <c r="B208" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>182</v>
+      </c>
+      <c r="B209" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>183</v>
+      </c>
+      <c r="B210" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>184</v>
+      </c>
+      <c r="B211" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>185</v>
+      </c>
+      <c r="B212" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>186</v>
+      </c>
+      <c r="B213" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>187</v>
+      </c>
+      <c r="B214" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>188</v>
+      </c>
+      <c r="B215" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>189</v>
+      </c>
+      <c r="B216" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>190</v>
+      </c>
+      <c r="B217" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>191</v>
+      </c>
+      <c r="B218" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>6</v>
+      </c>
+      <c r="B219" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>8</v>
+      </c>
+      <c r="B220" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>9</v>
+      </c>
+      <c r="B221" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>10</v>
+      </c>
+      <c r="B222" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>11</v>
+      </c>
+      <c r="B223" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>12</v>
+      </c>
+      <c r="B224" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>13</v>
+      </c>
+      <c r="B225" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>14</v>
+      </c>
+      <c r="B226" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>15</v>
+      </c>
+      <c r="B227" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>16</v>
+      </c>
+      <c r="B228" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>17</v>
+      </c>
+      <c r="B229" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>18</v>
+      </c>
+      <c r="B230" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>19</v>
+      </c>
+      <c r="B231" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>20</v>
+      </c>
+      <c r="B232" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>21</v>
+      </c>
+      <c r="B233" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>22</v>
+      </c>
+      <c r="B234" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>23</v>
+      </c>
+      <c r="B235" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>24</v>
+      </c>
+      <c r="B236" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>25</v>
+      </c>
+      <c r="B237" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>26</v>
+      </c>
+      <c r="B238" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>27</v>
+      </c>
+      <c r="B239" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>28</v>
+      </c>
+      <c r="B240" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>29</v>
+      </c>
+      <c r="B241" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>30</v>
+      </c>
+      <c r="B242" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>31</v>
+      </c>
+      <c r="B243" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>32</v>
+      </c>
+      <c r="B244" t="s">
+        <v>210</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:B8">
-    <sortState ref="A3:B8">
-      <sortCondition ref="B2:B8"/>
-    </sortState>
-  </autoFilter>
   <sortState ref="A1:B8">
     <sortCondition ref="A2"/>
   </sortState>
@@ -628,59 +2986,82 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -692,47 +3073,83 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2</v>
-      </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -743,103 +3160,135 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>196</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>192</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
+      <c r="A3">
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
+      <c r="A4">
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
+      <c r="A5">
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/new_folder/columns_group.xlsx
+++ b/new_folder/columns_group.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\DB部門\1A_風險分析\_HJK\TQ_Analytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2022011702\Desktop\Leo\TQ_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12390"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12390" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="group" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="merge_keys" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">group!$A$2:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">group!$A$1:$B$218</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="220">
   <si>
     <t>OD</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -680,11 +680,43 @@
     <t>TWN/APISTKATTR</t>
   </si>
   <si>
-    <t>fin_auditor</t>
+    <t>API_CODE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>API_CODE</t>
+    <t>CHN_NAMES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>財務-董事決議數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>財務-自結數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>財務-財簽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票日資料表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月營收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>籌碼資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集保資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股票屬性資料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1015,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B244"/>
+  <dimension ref="A1:B218"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
@@ -2764,214 +2796,6 @@
       </c>
       <c r="B218" t="s">
         <v>174</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>6</v>
-      </c>
-      <c r="B219" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>8</v>
-      </c>
-      <c r="B220" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>9</v>
-      </c>
-      <c r="B221" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>10</v>
-      </c>
-      <c r="B222" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>11</v>
-      </c>
-      <c r="B223" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>12</v>
-      </c>
-      <c r="B224" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>13</v>
-      </c>
-      <c r="B225" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>14</v>
-      </c>
-      <c r="B226" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>15</v>
-      </c>
-      <c r="B227" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>16</v>
-      </c>
-      <c r="B228" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>17</v>
-      </c>
-      <c r="B229" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>18</v>
-      </c>
-      <c r="B230" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>19</v>
-      </c>
-      <c r="B231" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>20</v>
-      </c>
-      <c r="B232" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>21</v>
-      </c>
-      <c r="B233" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>22</v>
-      </c>
-      <c r="B234" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>23</v>
-      </c>
-      <c r="B235" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>24</v>
-      </c>
-      <c r="B236" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A237" t="s">
-        <v>25</v>
-      </c>
-      <c r="B237" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A238" t="s">
-        <v>26</v>
-      </c>
-      <c r="B238" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A239" t="s">
-        <v>27</v>
-      </c>
-      <c r="B239" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A240" t="s">
-        <v>28</v>
-      </c>
-      <c r="B240" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
-        <v>29</v>
-      </c>
-      <c r="B241" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
-        <v>30</v>
-      </c>
-      <c r="B242" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>31</v>
-      </c>
-      <c r="B243" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>32</v>
-      </c>
-      <c r="B244" t="s">
-        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2997,7 +2821,7 @@
         <v>200</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3073,88 +2897,117 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>200</v>
       </c>
       <c r="B1" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>192</v>
       </c>
       <c r="B3" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
       <c r="B4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="B5" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>59</v>
       </c>
       <c r="B6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>91</v>
       </c>
       <c r="B7" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>151</v>
       </c>
       <c r="B8" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>174</v>
       </c>
       <c r="B9" t="s">
         <v>209</v>
+      </c>
+      <c r="C9" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
